--- a/RejestrPomiarow.xlsx
+++ b/RejestrPomiarow.xlsx
@@ -5,12 +5,13 @@
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loope\Documents\ProjektKlucze\09052026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nivm570\RES_zasoby_P01\Kontrola Momentu Dokręcania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6EA26C-54E3-4D37-A8C8-E850873DC9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABC74BC-4FEC-4F9B-A194-F73BB30B131B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="t65E4297jI8XJTt5/1K7N+vRj46pe+z/leCnLE8njEhePB+5LAUyQW3RAy56kjHoFLj5h4d0eojTRaxnw7bSyw==" workbookSaltValue="EKQl3iMDZVOa5zFuqE04vg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wyniki" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="84">
   <si>
     <t>Data</t>
   </si>
@@ -265,6 +266,15 @@
   </si>
   <si>
     <t>-95-5-</t>
+  </si>
+  <si>
+    <t>R0022</t>
+  </si>
+  <si>
+    <t>WKRĘTAK DYNAMOMETRYCZNY 2</t>
+  </si>
+  <si>
+    <t>r0022</t>
   </si>
 </sst>
 </file>
@@ -496,8 +506,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaWynikow" displayName="TabelaWynikow" ref="A1:Q112" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
-  <autoFilter ref="A1:Q112" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaWynikow" displayName="TabelaWynikow" ref="A1:Q123" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+  <autoFilter ref="A1:Q123" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Data" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Czas" dataDxfId="22"/>
@@ -807,8 +817,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Arkusz1"/>
-  <dimension ref="A1:Q112"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q123"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
     <col min="2" max="2" width="12" style="7" customWidth="1"/>
@@ -816,14 +826,14 @@
     <col min="4" max="4" width="16" style="3" customWidth="1"/>
     <col min="5" max="5" width="28" style="3" customWidth="1"/>
     <col min="6" max="6" width="14" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.21875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" style="3" customWidth="1"/>
     <col min="8" max="13" width="12" style="3" customWidth="1"/>
     <col min="14" max="16" width="10" style="3" customWidth="1"/>
     <col min="17" max="17" width="16" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.77734375" style="3"/>
+    <col min="18" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -876,7 +886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -923,7 +933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -973,7 +983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1023,7 +1033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>46128</v>
       </c>
@@ -1070,7 +1080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>46128</v>
       </c>
@@ -1120,7 +1130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>46128</v>
       </c>
@@ -1170,7 +1180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>46128</v>
       </c>
@@ -1220,7 +1230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>46128</v>
       </c>
@@ -1264,7 +1274,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>46128</v>
       </c>
@@ -1314,7 +1324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>46128</v>
       </c>
@@ -1361,7 +1371,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>46128</v>
       </c>
@@ -1411,7 +1421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>46128</v>
       </c>
@@ -1461,7 +1471,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>46128</v>
       </c>
@@ -1505,7 +1515,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>46128</v>
       </c>
@@ -1555,7 +1565,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>46128</v>
       </c>
@@ -1605,7 +1615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>46128</v>
       </c>
@@ -1652,7 +1662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>46128</v>
       </c>
@@ -1699,7 +1709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>46128</v>
       </c>
@@ -1749,7 +1759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>46128</v>
       </c>
@@ -1799,7 +1809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>46128</v>
       </c>
@@ -1846,7 +1856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>46128</v>
       </c>
@@ -1896,7 +1906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>46128</v>
       </c>
@@ -1946,7 +1956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>46128</v>
       </c>
@@ -1993,7 +2003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>46128</v>
       </c>
@@ -2043,7 +2053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>46128</v>
       </c>
@@ -2093,7 +2103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>46128</v>
       </c>
@@ -2143,7 +2153,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>46128</v>
       </c>
@@ -2193,7 +2203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>46128</v>
       </c>
@@ -2240,7 +2250,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>46128</v>
       </c>
@@ -2284,7 +2294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>46128</v>
       </c>
@@ -2334,7 +2344,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>46128</v>
       </c>
@@ -2384,7 +2394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>46128</v>
       </c>
@@ -2425,7 +2435,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>46128</v>
       </c>
@@ -2472,7 +2482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>46128</v>
       </c>
@@ -2519,7 +2529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>46128</v>
       </c>
@@ -2566,7 +2576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>46128</v>
       </c>
@@ -2613,7 +2623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>46128</v>
       </c>
@@ -2663,7 +2673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>46128</v>
       </c>
@@ -2713,7 +2723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>46132</v>
       </c>
@@ -2763,7 +2773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>46132</v>
       </c>
@@ -2813,7 +2823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>46132</v>
       </c>
@@ -2860,7 +2870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>46132</v>
       </c>
@@ -2907,7 +2917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>46132</v>
       </c>
@@ -2954,7 +2964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>46132</v>
       </c>
@@ -3004,7 +3014,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>46132</v>
       </c>
@@ -3051,7 +3061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>46132</v>
       </c>
@@ -3101,7 +3111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>46132</v>
       </c>
@@ -3151,7 +3161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>46133</v>
       </c>
@@ -3201,7 +3211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>46140</v>
       </c>
@@ -3242,7 +3252,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>46140</v>
       </c>
@@ -3289,7 +3299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>46141</v>
       </c>
@@ -3339,7 +3349,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>46146</v>
       </c>
@@ -3389,7 +3399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>46146</v>
       </c>
@@ -3439,7 +3449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>46146</v>
       </c>
@@ -3489,7 +3499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>46146</v>
       </c>
@@ -3539,7 +3549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>46146</v>
       </c>
@@ -3589,7 +3599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>46146</v>
       </c>
@@ -3639,7 +3649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>46146</v>
       </c>
@@ -3689,7 +3699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>46146</v>
       </c>
@@ -3739,7 +3749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>46146</v>
       </c>
@@ -3789,7 +3799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>46146</v>
       </c>
@@ -3839,7 +3849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>46146</v>
       </c>
@@ -3889,7 +3899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>46147</v>
       </c>
@@ -3939,7 +3949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>46147</v>
       </c>
@@ -3989,7 +3999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>46147</v>
       </c>
@@ -4039,7 +4049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>46147</v>
       </c>
@@ -4089,7 +4099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>46147</v>
       </c>
@@ -4139,7 +4149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>46147</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>46147</v>
       </c>
@@ -4239,7 +4249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>46147</v>
       </c>
@@ -4289,7 +4299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>46147</v>
       </c>
@@ -4339,7 +4349,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>46147</v>
       </c>
@@ -4389,7 +4399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>46147</v>
       </c>
@@ -4439,7 +4449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>46147</v>
       </c>
@@ -4489,7 +4499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>46147</v>
       </c>
@@ -4539,7 +4549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>46147</v>
       </c>
@@ -4589,7 +4599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>46147</v>
       </c>
@@ -4639,7 +4649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>46147</v>
       </c>
@@ -4689,7 +4699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>46147</v>
       </c>
@@ -4739,7 +4749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>46147</v>
       </c>
@@ -4789,7 +4799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>46147</v>
       </c>
@@ -4839,7 +4849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>46147</v>
       </c>
@@ -4889,7 +4899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>46148</v>
       </c>
@@ -4939,7 +4949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>46149</v>
       </c>
@@ -4989,7 +4999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>46149</v>
       </c>
@@ -5039,7 +5049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>46150</v>
       </c>
@@ -5089,7 +5099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>46150</v>
       </c>
@@ -5139,7 +5149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>46150</v>
       </c>
@@ -5189,7 +5199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>46150</v>
       </c>
@@ -5239,7 +5249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>46150</v>
       </c>
@@ -5289,7 +5299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>46150</v>
       </c>
@@ -5339,7 +5349,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>46150</v>
       </c>
@@ -5389,7 +5399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>46150</v>
       </c>
@@ -5439,7 +5449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>46150</v>
       </c>
@@ -5489,7 +5499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>46150</v>
       </c>
@@ -5539,7 +5549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>46150</v>
       </c>
@@ -5589,7 +5599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>46150</v>
       </c>
@@ -5639,7 +5649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>46150</v>
       </c>
@@ -5689,7 +5699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" s="6">
         <v>46150</v>
       </c>
@@ -5739,7 +5749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" s="6">
         <v>46150</v>
       </c>
@@ -5789,7 +5799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" s="6">
         <v>46150</v>
       </c>
@@ -5839,7 +5849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103" s="6">
         <v>46150</v>
       </c>
@@ -5889,7 +5899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104" s="6">
         <v>46150</v>
       </c>
@@ -5939,7 +5949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105" s="6">
         <v>46150</v>
       </c>
@@ -5989,7 +5999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106" s="6">
         <v>46151</v>
       </c>
@@ -6039,7 +6049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107" s="6">
         <v>46151</v>
       </c>
@@ -6089,7 +6099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108" s="6">
         <v>46151</v>
       </c>
@@ -6139,7 +6149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" s="6">
         <v>46151</v>
       </c>
@@ -6189,7 +6199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" s="6">
         <v>46151</v>
       </c>
@@ -6239,7 +6249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111" s="6">
         <v>46151</v>
       </c>
@@ -6289,7 +6299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112" s="6">
         <v>46151</v>
       </c>
@@ -6336,6 +6346,556 @@
         <v>24</v>
       </c>
       <c r="Q112" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A113" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B113" s="7">
+        <v>0.68836805555555558</v>
+      </c>
+      <c r="C113" s="3">
+        <v>5656</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H113" s="3">
+        <v>7</v>
+      </c>
+      <c r="J113" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="K113" s="3">
+        <v>7</v>
+      </c>
+      <c r="L113" s="3">
+        <v>7</v>
+      </c>
+      <c r="M113" s="3">
+        <v>7</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P113" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q113" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B114" s="7">
+        <v>0.43607638888888889</v>
+      </c>
+      <c r="C114" s="3">
+        <v>5656</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H114" s="3">
+        <v>1</v>
+      </c>
+      <c r="J114" s="3">
+        <v>6</v>
+      </c>
+      <c r="K114" s="3">
+        <v>1</v>
+      </c>
+      <c r="L114" s="3">
+        <v>1</v>
+      </c>
+      <c r="M114" s="3">
+        <v>1</v>
+      </c>
+      <c r="N114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q114" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A115" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B115" s="7">
+        <v>0.4369675925925926</v>
+      </c>
+      <c r="C115" s="3">
+        <v>6565</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H115" s="3">
+        <v>2</v>
+      </c>
+      <c r="J115" s="3">
+        <v>6</v>
+      </c>
+      <c r="K115" s="3">
+        <v>2</v>
+      </c>
+      <c r="L115" s="3">
+        <v>2</v>
+      </c>
+      <c r="M115" s="3">
+        <v>2</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q115" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A116" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B116" s="7">
+        <v>0.43975694444444446</v>
+      </c>
+      <c r="C116" s="3">
+        <v>5656</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H116" s="3">
+        <v>2</v>
+      </c>
+      <c r="J116" s="3">
+        <v>6</v>
+      </c>
+      <c r="K116" s="3">
+        <v>2</v>
+      </c>
+      <c r="L116" s="3">
+        <v>2</v>
+      </c>
+      <c r="M116" s="3">
+        <v>2</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q116" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A117" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B117" s="7">
+        <v>0.44005787037037036</v>
+      </c>
+      <c r="C117" s="3">
+        <v>5656</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H117" s="3">
+        <v>1</v>
+      </c>
+      <c r="J117" s="3">
+        <v>6</v>
+      </c>
+      <c r="K117" s="3">
+        <v>1</v>
+      </c>
+      <c r="L117" s="3">
+        <v>1</v>
+      </c>
+      <c r="M117" s="3">
+        <v>1</v>
+      </c>
+      <c r="N117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q117" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A118" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B118" s="7">
+        <v>0.44026620370370373</v>
+      </c>
+      <c r="C118" s="3">
+        <v>5656</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H118" s="3">
+        <v>2</v>
+      </c>
+      <c r="J118" s="3">
+        <v>6</v>
+      </c>
+      <c r="K118" s="3">
+        <v>2</v>
+      </c>
+      <c r="L118" s="3">
+        <v>2</v>
+      </c>
+      <c r="M118" s="3">
+        <v>2</v>
+      </c>
+      <c r="N118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q118" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A119" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B119" s="7">
+        <v>0.44351851851851853</v>
+      </c>
+      <c r="C119" s="3">
+        <v>6565</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H119" s="3">
+        <v>1</v>
+      </c>
+      <c r="J119" s="3">
+        <v>6</v>
+      </c>
+      <c r="K119" s="3">
+        <v>1</v>
+      </c>
+      <c r="L119" s="3">
+        <v>1</v>
+      </c>
+      <c r="M119" s="3">
+        <v>1</v>
+      </c>
+      <c r="N119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q119" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A120" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B120" s="7">
+        <v>0.50935185185185183</v>
+      </c>
+      <c r="C120" s="3">
+        <v>56565</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H120" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J120" s="3">
+        <v>6</v>
+      </c>
+      <c r="K120" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L120" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="M120" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="N120" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P120" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q120" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A121" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B121" s="7">
+        <v>0.5096180555555555</v>
+      </c>
+      <c r="C121" s="3">
+        <v>56565</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H121" s="3">
+        <v>2</v>
+      </c>
+      <c r="J121" s="3">
+        <v>6</v>
+      </c>
+      <c r="K121" s="3">
+        <v>2</v>
+      </c>
+      <c r="L121" s="3">
+        <v>2</v>
+      </c>
+      <c r="M121" s="3">
+        <v>2</v>
+      </c>
+      <c r="N121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q121" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A122" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B122" s="7">
+        <v>0.61290509259259263</v>
+      </c>
+      <c r="C122" s="3">
+        <v>56565</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H122" s="3">
+        <v>1</v>
+      </c>
+      <c r="J122" s="3">
+        <v>6</v>
+      </c>
+      <c r="K122" s="3">
+        <v>1</v>
+      </c>
+      <c r="L122" s="3">
+        <v>1</v>
+      </c>
+      <c r="M122" s="3">
+        <v>1</v>
+      </c>
+      <c r="N122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q122" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B123" s="7">
+        <v>0.61311342592592588</v>
+      </c>
+      <c r="C123" s="3">
+        <v>56565</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H123" s="3">
+        <v>1</v>
+      </c>
+      <c r="J123" s="3">
+        <v>6</v>
+      </c>
+      <c r="K123" s="3">
+        <v>1</v>
+      </c>
+      <c r="L123" s="3">
+        <v>1</v>
+      </c>
+      <c r="M123" s="3">
+        <v>1</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q123" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6429,37 +6989,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Arkusz2"/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -6473,19 +7033,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BDBFBB-A168-4E0B-AFF6-84297AC4208C}">
   <sheetPr codeName="Arkusz3"/>
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>46</v>
       </c>
